--- a/registro de supuestos/Registro_Supuestos_Overfore_v1.6.xlsx
+++ b/registro de supuestos/Registro_Supuestos_Overfore_v1.6.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>40 supuestos: 14 decisiones del numeral 16.1, 7 vacíos adicionales identificados por el proponente, 2 supuestos del alcance y 17 umbrales y definiciones del proponente</t>
+          <t>41 supuestos: 14 decisiones del numeral 16.1, 7 vacíos adicionales identificados por el proponente, 2 supuestos del alcance y 18 umbrales y definiciones del proponente</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>1.6 — 2 de septiembre de 2026. Incorpora SUP-40, la cota de 35.000 eventos de la cola de reconciliación de 48 horas que el Subdocumento 4.1 v4.2 define en su apartado 12.6.</t>
+          <t>1.6 — 2 de septiembre de 2026. Incorpora SUP-40, la cota de 35.000 eventos de la cola de reconciliación de 48 horas —de faena completa, no por sitio— que el Subdocumento 4.1 v4.2 define en su apartado 12.6. Revisión de consistencia del 4 de septiembre de 2026: se completan las columnas vacías de SUP-40; se corrige en SUP-08 la atribución de las 8.500 personas, que son el total con acceso en detención mayor y no el universo contratista, que es de 6.700; se reapuntan SUP-38 y SUP-39 del Subdocumento 4.1 v3.1 a la v4.2, cuya renumeración dejó obsoletas ambas remisiones; y se incorpora SUP-41, la selección de señales del historiador que se ingestan de forma continua.</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Son 2.400 personas en régimen y hasta 8.500 en detención mayor, de unas 90 empresas, sin correo corporativo (Cap. 14.1 y 16.1 n.º 8). Crear identidad corporativa por persona es inviable con un equipo de TI de once personas (restricción n.º 10). RT-12.12 exige un mecanismo autoservido para personas usuarias externas.</t>
+          <t>Son 2.400 personas contratistas en régimen y hasta 6.700 en detención mayor, de unas 90 empresas, sin correo corporativo. Las 8.500 del Cap. 14.1 son el total de personas con acceso a la faena en ese peak e incluyen a las 1.780 propias, que la restricción n.º 9 federa (Cap. 2.4, 14.1 y 16.1 n.º 8). Crear identidad corporativa por persona es inviable con un equipo de TI de once personas (restricción n.º 10). RT-12.12 exige un mecanismo autoservido para personas usuarias externas.</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Si el CLIENTE exige federación estricta también para externos, hay que provisionar entre 2.400 y 8.500 identidades con un equipo de TI de once personas.</t>
+          <t>Si el CLIENTE exige federación estricta también para externos, hay que provisionar entre 2.400 y 6.700 identidades de personas contratistas con un equipo de TI de once personas.</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>Corte controlado de 48 horas del apartado 9.2 del Subdocumento 4.1, verificando que la caché sostiene la validación en portería dentro de 1,5 segundos y que, vencida la vigencia, el nodo deja de admitir. Consulta al CLIENTE sobre la exigibilidad de la revocación durante el corte.</t>
+          <t>Corte controlado de 48 horas del apartado 11.2 del Subdocumento 4.1 v4.2, verificando que la caché sostiene la validación en portería dentro de 1,5 segundos y que, vencida la vigencia, el nodo deja de admitir. Consulta al CLIENTE sobre la exigibilidad de la revocación durante el corte.</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>Subdocumento 4.1 v3.1, apartado 11.1</t>
+          <t>Subdocumento 4.1 v4.2, apartado 13.1</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>Subdocumento 4.1 v3.1, apartado 16.4</t>
+          <t>Subdocumento 4.1 v4.2, apartado 16.4</t>
         </is>
       </c>
       <c r="J40" s="6" t="inlineStr">
@@ -2716,6 +2716,78 @@
       <c r="F41" s="6" t="inlineStr">
         <is>
           <t>Corte controlado de 48 horas en la marcha blanca de la Etapa 1 (RT-03.19), midiendo el volumen real acumulado y el tiempo efectivo de drenaje sobre los cuatro nodos de borde.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Marcha blanca Etapa 1</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>RNF-CAP-006, RF-DES-011, RF-DES-004 · Criterio n.º 13</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Subdocumento 4.1 v4.2, apartado 12.6</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SUP-41</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Umbral definido por el proponente</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>De las ~14.500 etiquetas de proceso que el historiador de planta declara hoy —16.000 en la proyección a tres años— se ingestan de forma continua ~5.000: las que alimentan la conciliación metalúrgica, la balanza de alimentación, el monitoreo ambiental y el cálculo de la huella de carbono. El resto permanece en el historiador, que no se reemplaza, y se lee por C-14 bajo demanda.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>El numeral 14.1 declara el universo de etiquetas, no cuáles debe capturar la solución. La ingesta continua de las 14.500 llevaría la capa de series de tiempo de 2 a ~5,7 TB al año sin que ningún criterio del Capítulo 18 lo exija, y el historiador sigue siendo la fuente para la señal que no se ingesta. La selección es, por tanto, definición del PROPONENTE.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Si el CLIENTE exige la ingesta completa, la capa de series de tiempo y el ancho de banda del enlace de planta se redimensionan al triple, con impacto en la Oferta Económica y en el Formulario T-11; no cambian los componentes ni los contratos de interfaz.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Levantamiento de las señales del historiador con la Superintendencia de Planta y Metalurgia, dentro de VAL-03 del Subdocumento 4.2, y consulta al CLIENTE en el período de consultas.</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Período de consultas y actividad temprana de la Etapa 1</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>RNF-CAP-007, RF-PES-002, RF-AMB-005 · Criterios n.º 3 y n.º 12</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Subdocumento 5 v2.1, apartado 4.6</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Abierto</t>
         </is>
       </c>
     </row>
